--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260923.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260923.xlsx
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>143,921</t>
+          <t>987,822</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>987,822</t>
+          <t>143,921</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>923,659</t>
+          <t>1,179,441</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,179,441</t>
+          <t>923,659</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,291,384</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>1,291,384</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>4,015,578</t>
+          <t>574,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>574,000</t>
+          <t>4,015,578</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>143,386</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>143,386</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,168,076</t>
+          <t>765,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>765,000</t>
+          <t>1,168,076</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>747,000</t>
+          <t>286,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>490,000</t>
+          <t>4,889,956</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>4,889,956</t>
+          <t>747,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>286,000</t>
+          <t>490,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,733,000</t>
+          <t>1,113,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,113,121</t>
+          <t>1,733,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>326,000</t>
+          <t>168,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>168,000</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>63,538</t>
+          <t>326,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>63,538</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
